--- a/_drafts/referentiel/Competences.xlsx
+++ b/_drafts/referentiel/Competences.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{D89B302D-F270-4664-B9F1-DC8C23906D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-6225" windowWidth="29040" windowHeight="15720" xr2:uid="{5E8D09BC-C3B7-4511-9990-F014C3BA6E49}"/>
+    <workbookView xWindow="-28935" yWindow="-6240" windowWidth="29070" windowHeight="15750" xr2:uid="{5E8D09BC-C3B7-4511-9990-F014C3BA6E49}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
